--- a/data_out/us_rstar_comparison.xlsx
+++ b/data_out/us_rstar_comparison.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K171"/>
+  <dimension ref="A1:K174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6335,6 +6335,99 @@
         </is>
       </c>
     </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Combined</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D172" t="n">
+        <v>3</v>
+      </c>
+      <c r="E172" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Combined</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="D173" t="n">
+        <v>3</v>
+      </c>
+      <c r="E173" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Combined</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="D174" t="n">
+        <v>3</v>
+      </c>
+      <c r="E174" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>xlsx</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_out/us_rstar_comparison.xlsx
+++ b/data_out/us_rstar_comparison.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K174"/>
+  <dimension ref="A1:N174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,45 +441,60 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>distributed_date</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>received_by_date</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>receipt_source_file</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>our_median</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>our_p25</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>our_p75</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>hartley_median</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>hartley_p25</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>hartley_p75</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>median_diff</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>abs_diff</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
@@ -496,15 +511,30 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2011-01-13</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2011-01-18</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>data_raw/2011-January_result.pdf</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -521,15 +551,30 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2011-03-03</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2011-03-07</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>data_raw/2011-March_result.pdf</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -546,15 +591,30 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2011-04-13</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2011-04-18</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>data_raw/2011-April_result.pdf</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -571,15 +631,30 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2011-06-09</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2011-06-13</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>data_raw/2011-June_result.pdf</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -596,15 +671,30 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2011-07-28</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2011-08-01</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>data_raw/2011-August_result.pdf</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -621,15 +711,30 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2011-09-08</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2011-09-12</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>data_raw/2011-September_result.pdf</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -646,15 +751,30 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2011-10-20</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2011-10-24</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>data_raw/2011-November_result.pdf</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -671,14 +791,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>4</v>
-      </c>
-      <c r="D9" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="E9" t="n">
-        <v>4</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2012-06-07</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2012-06-11</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>data_raw/2012-June_result.pdf</t>
+        </is>
       </c>
       <c r="F9" t="n">
         <v>4</v>
@@ -690,12 +816,21 @@
         <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="inlineStr">
+        <v>3.94</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -711,18 +846,21 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="n">
-        <v>4</v>
-      </c>
-      <c r="G10" t="n">
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" t="n">
         <v>3.75</v>
       </c>
-      <c r="H10" t="n">
-        <v>4</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="n">
+        <v>4</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -735,14 +873,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>4</v>
-      </c>
-      <c r="D11" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="E11" t="n">
-        <v>4</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2012-07-19</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2012-07-23</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>data_raw/2012-august_result.pdf</t>
+        </is>
       </c>
       <c r="F11" t="n">
         <v>4</v>
@@ -754,12 +898,21 @@
         <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr">
+        <v>3.75</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -776,14 +929,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>4</v>
-      </c>
-      <c r="D12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="E12" t="n">
-        <v>4</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2012-08-31</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2012-09-04</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>data_raw/2012-September_result.pdf</t>
+        </is>
       </c>
       <c r="F12" t="n">
         <v>4</v>
@@ -795,12 +954,21 @@
         <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr">
+        <v>3.75</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -817,14 +985,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>4</v>
-      </c>
-      <c r="D13" t="n">
-        <v>4</v>
-      </c>
-      <c r="E13" t="n">
-        <v>4</v>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2012-10-11</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2012-10-15</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>data_raw/2012-October_result.pdf</t>
+        </is>
       </c>
       <c r="F13" t="n">
         <v>4</v>
@@ -836,12 +1010,21 @@
         <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -857,18 +1040,21 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="n">
-        <v>4</v>
-      </c>
-      <c r="G14" t="n">
-        <v>4</v>
-      </c>
-      <c r="H14" t="n">
-        <v>4</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -881,14 +1067,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>4</v>
-      </c>
-      <c r="D15" t="n">
-        <v>4</v>
-      </c>
-      <c r="E15" t="n">
-        <v>4</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2012-11-29</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2012-12-03</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>data_raw/2012-December_result.pdf</t>
+        </is>
       </c>
       <c r="F15" t="n">
         <v>4</v>
@@ -900,12 +1092,21 @@
         <v>4</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -922,14 +1123,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>4</v>
-      </c>
-      <c r="D16" t="n">
-        <v>4</v>
-      </c>
-      <c r="E16" t="n">
-        <v>4</v>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2013-01-17</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2013-01-22</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>data_raw/2013-January_result.pdf</t>
+        </is>
       </c>
       <c r="F16" t="n">
         <v>4</v>
@@ -941,12 +1148,21 @@
         <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -962,18 +1178,21 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="n">
-        <v>4</v>
-      </c>
-      <c r="G17" t="n">
-        <v>4</v>
-      </c>
-      <c r="H17" t="n">
-        <v>4</v>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -986,14 +1205,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>4</v>
-      </c>
-      <c r="D18" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="E18" t="n">
-        <v>4</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2013-03-07</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2013-03-11</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>data_raw/2013-March_result.pdf</t>
+        </is>
       </c>
       <c r="F18" t="n">
         <v>4</v>
@@ -1005,12 +1230,21 @@
         <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
+        <v>3.75</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -1027,14 +1261,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>4</v>
-      </c>
-      <c r="D19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="E19" t="n">
-        <v>4</v>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2013-04-18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2013-04-22</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>data_raw/2013-April_result.pdf</t>
+        </is>
       </c>
       <c r="F19" t="n">
         <v>4</v>
@@ -1046,12 +1286,21 @@
         <v>4</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr">
+        <v>3.75</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -1067,18 +1316,21 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="n">
-        <v>4</v>
-      </c>
-      <c r="G20" t="n">
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>4</v>
+      </c>
+      <c r="J20" t="n">
         <v>3.75</v>
       </c>
-      <c r="H20" t="n">
-        <v>4</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="n">
+        <v>4</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1091,14 +1343,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C21" t="n">
-        <v>4</v>
-      </c>
-      <c r="D21" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="E21" t="n">
-        <v>4</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2013-06-06</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2013-06-10</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>data_raw/2013-June_result.pdf</t>
+        </is>
       </c>
       <c r="F21" t="n">
         <v>4</v>
@@ -1110,12 +1368,21 @@
         <v>4</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="inlineStr">
+        <v>3.75</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -1132,14 +1399,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>4</v>
-      </c>
-      <c r="D22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E22" t="n">
-        <v>4</v>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2013-07-17</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2013-07-22</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>data_raw/2013-July_result.pdf</t>
+        </is>
       </c>
       <c r="F22" t="n">
         <v>4</v>
@@ -1151,12 +1424,21 @@
         <v>4</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr">
+        <v>3.5</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -1172,18 +1454,21 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="n">
-        <v>4</v>
-      </c>
-      <c r="G23" t="n">
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="n">
+        <v>4</v>
+      </c>
+      <c r="J23" t="n">
         <v>3.5</v>
       </c>
-      <c r="H23" t="n">
-        <v>4</v>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="n">
+        <v>4</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1196,14 +1481,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>4</v>
-      </c>
-      <c r="D24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E24" t="n">
-        <v>4</v>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2013-09-05</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2013-09-09</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>data_raw/2013-September_result.pdf</t>
+        </is>
       </c>
       <c r="F24" t="n">
         <v>4</v>
@@ -1215,12 +1506,21 @@
         <v>4</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
+        <v>3.5</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -1237,14 +1537,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C25" t="n">
-        <v>4</v>
-      </c>
-      <c r="D25" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="E25" t="n">
-        <v>4</v>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2013-10-17</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2013-10-22</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>data_raw/2013-October_result.pdf</t>
+        </is>
       </c>
       <c r="F25" t="n">
         <v>4</v>
@@ -1256,12 +1562,21 @@
         <v>4</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
+        <v>3.75</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -1277,18 +1592,21 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="n">
-        <v>4</v>
-      </c>
-      <c r="G26" t="n">
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="n">
+        <v>4</v>
+      </c>
+      <c r="J26" t="n">
         <v>3.75</v>
       </c>
-      <c r="H26" t="n">
-        <v>4</v>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="n">
+        <v>4</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1301,14 +1619,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C27" t="n">
-        <v>4</v>
-      </c>
-      <c r="D27" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="E27" t="n">
-        <v>4</v>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2013-12-05</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2013-12-09</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>data_raw/2013-December_result.pdf</t>
+        </is>
       </c>
       <c r="F27" t="n">
         <v>4</v>
@@ -1320,12 +1644,21 @@
         <v>4</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="inlineStr">
+        <v>3.75</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -1342,14 +1675,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C28" t="n">
-        <v>4</v>
-      </c>
-      <c r="D28" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="E28" t="n">
-        <v>4</v>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2014-01-16</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2014-01-21</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>data_raw/2014-January_result.pdf</t>
+        </is>
       </c>
       <c r="F28" t="n">
         <v>4</v>
@@ -1361,12 +1700,21 @@
         <v>4</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="inlineStr">
+        <v>3.75</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -1382,18 +1730,21 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="n">
-        <v>4</v>
-      </c>
-      <c r="G29" t="n">
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="n">
+        <v>4</v>
+      </c>
+      <c r="J29" t="n">
         <v>3.75</v>
       </c>
-      <c r="H29" t="n">
-        <v>4</v>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="n">
+        <v>4</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1406,14 +1757,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D30" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="E30" t="n">
-        <v>4</v>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2014-03-06</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2014-03-10</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>data_raw/2014-March_result.pdf</t>
+        </is>
       </c>
       <c r="F30" t="n">
         <v>3.75</v>
@@ -1425,12 +1782,21 @@
         <v>4</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="inlineStr">
+        <v>3.75</v>
+      </c>
+      <c r="K30" t="n">
+        <v>4</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -1447,14 +1813,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C31" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D31" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E31" t="n">
-        <v>4</v>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2014-04-17</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2014-04-22</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>data_raw/2014-April_result.pdf</t>
+        </is>
       </c>
       <c r="F31" t="n">
         <v>3.75</v>
@@ -1466,12 +1838,21 @@
         <v>4</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="inlineStr">
+        <v>3.5</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -1487,18 +1868,21 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="n">
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="n">
         <v>3.75</v>
       </c>
-      <c r="G32" t="n">
+      <c r="J32" t="n">
         <v>3.5</v>
       </c>
-      <c r="H32" t="n">
-        <v>4</v>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="n">
+        <v>4</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1511,14 +1895,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C33" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D33" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E33" t="n">
-        <v>4</v>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2014-06-05</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2014-06-09</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>data_raw/2014-June_result.pdf</t>
+        </is>
       </c>
       <c r="F33" t="n">
         <v>3.5</v>
@@ -1530,12 +1920,21 @@
         <v>4</v>
       </c>
       <c r="I33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K33" t="n">
+        <v>4</v>
+      </c>
+      <c r="L33" t="n">
         <v>-4.440892098500626e-16</v>
       </c>
-      <c r="J33" t="n">
+      <c r="M33" t="n">
         <v>4.440892098500626e-16</v>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -1552,14 +1951,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C34" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D34" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E34" t="n">
-        <v>4</v>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2014-07-16</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2014-07-21</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>data_raw/2014-July_result.pdf</t>
+        </is>
       </c>
       <c r="F34" t="n">
         <v>3.5</v>
@@ -1571,12 +1976,21 @@
         <v>4</v>
       </c>
       <c r="I34" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K34" t="n">
+        <v>4</v>
+      </c>
+      <c r="L34" t="n">
         <v>-4.440892098500626e-16</v>
       </c>
-      <c r="J34" t="n">
+      <c r="M34" t="n">
         <v>4.440892098500626e-16</v>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -1592,18 +2006,21 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="n">
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="n">
         <v>3.5</v>
       </c>
-      <c r="G35" t="n">
+      <c r="J35" t="n">
         <v>3.5</v>
       </c>
-      <c r="H35" t="n">
-        <v>4</v>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="n">
+        <v>4</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1616,14 +2033,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C36" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D36" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E36" t="n">
-        <v>4</v>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2014-09-04</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2014-09-08</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>data_raw/2014-September_result.pdf</t>
+        </is>
       </c>
       <c r="F36" t="n">
         <v>3.5</v>
@@ -1635,12 +2058,21 @@
         <v>4</v>
       </c>
       <c r="I36" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K36" t="n">
+        <v>4</v>
+      </c>
+      <c r="L36" t="n">
         <v>-4.440892098500626e-16</v>
       </c>
-      <c r="J36" t="n">
+      <c r="M36" t="n">
         <v>4.440892098500626e-16</v>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -1657,14 +2089,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C37" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D37" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E37" t="n">
-        <v>4</v>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2014-10-16</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2014-10-20</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>data_raw/2014-October_result.pdf</t>
+        </is>
       </c>
       <c r="F37" t="n">
         <v>3.5</v>
@@ -1676,12 +2114,21 @@
         <v>4</v>
       </c>
       <c r="I37" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K37" t="n">
+        <v>4</v>
+      </c>
+      <c r="L37" t="n">
         <v>-4.440892098500626e-16</v>
       </c>
-      <c r="J37" t="n">
+      <c r="M37" t="n">
         <v>4.440892098500626e-16</v>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -1697,18 +2144,21 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="n">
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="n">
         <v>3.5</v>
       </c>
-      <c r="G38" t="n">
+      <c r="J38" t="n">
         <v>3.5</v>
       </c>
-      <c r="H38" t="n">
-        <v>4</v>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="n">
+        <v>4</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1721,14 +2171,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C39" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D39" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E39" t="n">
-        <v>4</v>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2014-12-04</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2014-12-08</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>data_raw/2014-December_result.pdf</t>
+        </is>
       </c>
       <c r="F39" t="n">
         <v>3.5</v>
@@ -1740,12 +2196,21 @@
         <v>4</v>
       </c>
       <c r="I39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K39" t="n">
+        <v>4</v>
+      </c>
+      <c r="L39" t="n">
         <v>-4.440892098500626e-16</v>
       </c>
-      <c r="J39" t="n">
+      <c r="M39" t="n">
         <v>4.440892098500626e-16</v>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -1762,14 +2227,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C40" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D40" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E40" t="n">
-        <v>4</v>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2015-01-15</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2015-01-20</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>data_raw/January-result.pdf</t>
+        </is>
       </c>
       <c r="F40" t="n">
         <v>3.5</v>
@@ -1781,12 +2252,21 @@
         <v>4</v>
       </c>
       <c r="I40" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J40" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K40" t="n">
+        <v>4</v>
+      </c>
+      <c r="L40" t="n">
         <v>-4.440892098500626e-16</v>
       </c>
-      <c r="J40" t="n">
+      <c r="M40" t="n">
         <v>4.440892098500626e-16</v>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -1802,18 +2282,21 @@
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
-      <c r="F41" t="n">
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="n">
         <v>3.5</v>
       </c>
-      <c r="G41" t="n">
+      <c r="J41" t="n">
         <v>3.5</v>
       </c>
-      <c r="H41" t="n">
+      <c r="K41" t="n">
         <v>3.75</v>
       </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1826,14 +2309,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C42" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D42" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="E42" t="n">
-        <v>3.75</v>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2015-03-05</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2015-03-09</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>data_raw/March-result.pdf</t>
+        </is>
       </c>
       <c r="F42" t="n">
         <v>3.5</v>
@@ -1845,12 +2334,21 @@
         <v>3.75</v>
       </c>
       <c r="I42" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J42" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K42" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L42" t="n">
         <v>-4.440892098500626e-16</v>
       </c>
-      <c r="J42" t="n">
+      <c r="M42" t="n">
         <v>4.440892098500626e-16</v>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -1867,14 +2365,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C43" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D43" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="E43" t="n">
-        <v>3.75</v>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2015-04-16</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2015-04-20</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>data_raw/April-result.pdf</t>
+        </is>
       </c>
       <c r="F43" t="n">
         <v>3.5</v>
@@ -1886,12 +2390,21 @@
         <v>3.75</v>
       </c>
       <c r="I43" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J43" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L43" t="n">
         <v>-4.440892098500626e-16</v>
       </c>
-      <c r="J43" t="n">
+      <c r="M43" t="n">
         <v>4.440892098500626e-16</v>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -1907,18 +2420,21 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
-      <c r="F44" t="n">
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="n">
         <v>3.5</v>
       </c>
-      <c r="G44" t="n">
+      <c r="J44" t="n">
         <v>3.25</v>
       </c>
-      <c r="H44" t="n">
+      <c r="K44" t="n">
         <v>3.75</v>
       </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1931,14 +2447,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C45" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D45" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="E45" t="n">
-        <v>3.75</v>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2015-06-04</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2015-06-08</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>data_raw/June-result.pdf</t>
+        </is>
       </c>
       <c r="F45" t="n">
         <v>3.5</v>
@@ -1950,12 +2472,21 @@
         <v>3.75</v>
       </c>
       <c r="I45" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J45" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K45" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L45" t="n">
         <v>-4.440892098500626e-16</v>
       </c>
-      <c r="J45" t="n">
+      <c r="M45" t="n">
         <v>4.440892098500626e-16</v>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -1972,14 +2503,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C46" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="D46" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="E46" t="n">
-        <v>3.75</v>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2015-07-15</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2015-07-20</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>data_raw/July-result.pdf</t>
+        </is>
       </c>
       <c r="F46" t="n">
         <v>3.38</v>
@@ -1991,12 +2528,21 @@
         <v>3.75</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="inlineStr">
+        <v>3.25</v>
+      </c>
+      <c r="K46" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -2012,18 +2558,21 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
-      <c r="F47" t="n">
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="n">
         <v>3.38</v>
       </c>
-      <c r="G47" t="n">
+      <c r="J47" t="n">
         <v>3.25</v>
       </c>
-      <c r="H47" t="n">
+      <c r="K47" t="n">
         <v>3.75</v>
       </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2036,14 +2585,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C48" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="D48" t="n">
-        <v>3</v>
-      </c>
-      <c r="E48" t="n">
-        <v>3.75</v>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2015-09-03</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2015-09-08</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>data_raw/Sep-results.pdf</t>
+        </is>
       </c>
       <c r="F48" t="n">
         <v>3.38</v>
@@ -2055,12 +2610,21 @@
         <v>3.75</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="K48" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -2076,18 +2640,21 @@
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="n">
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="n">
         <v>3.25</v>
       </c>
-      <c r="G49" t="n">
-        <v>3</v>
-      </c>
-      <c r="H49" t="n">
+      <c r="J49" t="n">
+        <v>3</v>
+      </c>
+      <c r="K49" t="n">
         <v>3.5</v>
       </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2099,18 +2666,21 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
-      <c r="F50" t="n">
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="n">
         <v>3.25</v>
       </c>
-      <c r="G50" t="n">
-        <v>3</v>
-      </c>
-      <c r="H50" t="n">
+      <c r="J50" t="n">
+        <v>3</v>
+      </c>
+      <c r="K50" t="n">
         <v>3.5</v>
       </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2123,14 +2693,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C51" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="D51" t="n">
-        <v>3</v>
-      </c>
-      <c r="E51" t="n">
-        <v>3.5</v>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2015-12-07</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>data_raw/Dec-2015-results.pdf</t>
+        </is>
       </c>
       <c r="F51" t="n">
         <v>3.25</v>
@@ -2142,12 +2718,21 @@
         <v>3.5</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="K51" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -2164,14 +2749,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C52" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="D52" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E52" t="n">
-        <v>3.5</v>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2016-01-14</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2016-01-19</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>data_raw/jan-2016-results.pdf</t>
+        </is>
       </c>
       <c r="F52" t="n">
         <v>3.25</v>
@@ -2183,12 +2774,21 @@
         <v>3.5</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" t="inlineStr">
+        <v>2.9</v>
+      </c>
+      <c r="K52" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -2204,18 +2804,21 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="n">
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="n">
         <v>3.25</v>
       </c>
-      <c r="G53" t="n">
+      <c r="J53" t="n">
         <v>2.9</v>
       </c>
-      <c r="H53" t="n">
+      <c r="K53" t="n">
         <v>3.5</v>
       </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2228,14 +2831,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C54" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="D54" t="n">
-        <v>3</v>
-      </c>
-      <c r="E54" t="n">
-        <v>3.38</v>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2016-03-03</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2016-03-07</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>data_raw/mar-2016-results.pdf</t>
+        </is>
       </c>
       <c r="F54" t="n">
         <v>3.25</v>
@@ -2247,12 +2856,21 @@
         <v>3.38</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="K54" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -2269,14 +2887,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C55" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="D55" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E55" t="n">
-        <v>3.25</v>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2016-04-14</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2016-04-18</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>data_raw/apr-2016-results.pdf</t>
+        </is>
       </c>
       <c r="F55" t="n">
         <v>3.25</v>
@@ -2288,12 +2912,21 @@
         <v>3.25</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="inlineStr">
+        <v>2.9</v>
+      </c>
+      <c r="K55" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -2309,18 +2942,21 @@
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
-      <c r="F56" t="n">
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="n">
         <v>3.25</v>
       </c>
-      <c r="G56" t="n">
+      <c r="J56" t="n">
         <v>2.9</v>
       </c>
-      <c r="H56" t="n">
+      <c r="K56" t="n">
         <v>3.25</v>
       </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2333,31 +2969,46 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C57" t="n">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2016-06-02</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2016-06-06</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>data_raw/jun-2016-results.pdf</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
         <v>3.25</v>
       </c>
-      <c r="D57" t="n">
+      <c r="G57" t="n">
         <v>3.25</v>
-      </c>
-      <c r="E57" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="F57" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="G57" t="n">
-        <v>2.75</v>
       </c>
       <c r="H57" t="n">
         <v>3.25</v>
       </c>
       <c r="I57" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="J57" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K57" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L57" t="n">
         <v>0.1199999999999997</v>
       </c>
-      <c r="J57" t="n">
+      <c r="M57" t="n">
         <v>0.1199999999999997</v>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -2374,14 +3025,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C58" t="n">
-        <v>3</v>
-      </c>
-      <c r="D58" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="E58" t="n">
-        <v>3.25</v>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2016-07-14</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2016-07-18</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>data_raw/jul-2016-results.pdf</t>
+        </is>
       </c>
       <c r="F58" t="n">
         <v>3</v>
@@ -2393,12 +3050,21 @@
         <v>3.25</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" t="inlineStr">
+        <v>2.63</v>
+      </c>
+      <c r="K58" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -2414,18 +3080,21 @@
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="n">
-        <v>3</v>
-      </c>
-      <c r="G59" t="n">
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="n">
+        <v>3</v>
+      </c>
+      <c r="J59" t="n">
         <v>2.63</v>
       </c>
-      <c r="H59" t="n">
+      <c r="K59" t="n">
         <v>3.25</v>
       </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2438,14 +3107,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C60" t="n">
-        <v>3</v>
-      </c>
-      <c r="D60" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E60" t="n">
-        <v>3</v>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2016-09-08</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2016-09-12</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>data_raw/sep-2016-results.pdf</t>
+        </is>
       </c>
       <c r="F60" t="n">
         <v>3</v>
@@ -2457,12 +3132,21 @@
         <v>3</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" t="inlineStr">
+        <v>2.5</v>
+      </c>
+      <c r="K60" t="n">
+        <v>3</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -2478,18 +3162,21 @@
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
-      <c r="F61" t="n">
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="n">
         <v>2.75</v>
       </c>
-      <c r="G61" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H61" t="n">
-        <v>3</v>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
+      <c r="J61" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K61" t="n">
+        <v>3</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2502,14 +3189,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C62" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="D62" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E62" t="n">
-        <v>3</v>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2016-10-20</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2016-10-24</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>data_raw/Nov-2016-SPD-Results.pdf</t>
+        </is>
       </c>
       <c r="F62" t="n">
         <v>2.75</v>
@@ -2521,12 +3214,21 @@
         <v>3</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" t="inlineStr">
+        <v>2.5</v>
+      </c>
+      <c r="K62" t="n">
+        <v>3</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -2543,14 +3245,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C63" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="D63" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E63" t="n">
-        <v>3</v>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2016-12-01</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2016-12-05</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>data_raw/Dec-2016-SPD-Results-Public-Release.pdf</t>
+        </is>
       </c>
       <c r="F63" t="n">
         <v>2.75</v>
@@ -2562,12 +3270,21 @@
         <v>3</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" t="inlineStr">
+        <v>2.5</v>
+      </c>
+      <c r="K63" t="n">
+        <v>3</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -2584,14 +3301,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C64" t="n">
-        <v>3</v>
-      </c>
-      <c r="D64" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E64" t="n">
-        <v>3</v>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2017-01-19</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2017-01-23</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>data_raw/Jan-2017-SPD-Results-Public-Release.pdf</t>
+        </is>
       </c>
       <c r="F64" t="n">
         <v>3</v>
@@ -2603,12 +3326,21 @@
         <v>3</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" t="inlineStr">
+        <v>2.5</v>
+      </c>
+      <c r="K64" t="n">
+        <v>3</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -2624,18 +3356,21 @@
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="n">
-        <v>3</v>
-      </c>
-      <c r="G65" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H65" t="n">
-        <v>3</v>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="n">
+        <v>3</v>
+      </c>
+      <c r="J65" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K65" t="n">
+        <v>3</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2648,31 +3383,46 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C66" t="n">
-        <v>3</v>
-      </c>
-      <c r="D66" t="n">
-        <v>3</v>
-      </c>
-      <c r="E66" t="n">
-        <v>3</v>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2017-03-02</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2017-03-06</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>data_raw/Mar-2017-SPD-Results-Public-Release.pdf</t>
+        </is>
       </c>
       <c r="F66" t="n">
         <v>3</v>
       </c>
       <c r="G66" t="n">
+        <v>3</v>
+      </c>
+      <c r="H66" t="n">
+        <v>3</v>
+      </c>
+      <c r="I66" t="n">
+        <v>3</v>
+      </c>
+      <c r="J66" t="n">
         <v>2.63</v>
       </c>
-      <c r="H66" t="n">
-        <v>3</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" t="inlineStr">
+      <c r="K66" t="n">
+        <v>3</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -2688,18 +3438,21 @@
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="n">
-        <v>3</v>
-      </c>
-      <c r="G67" t="n">
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="n">
+        <v>3</v>
+      </c>
+      <c r="J67" t="n">
         <v>2.63</v>
       </c>
-      <c r="H67" t="n">
-        <v>3</v>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="n">
+        <v>3</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2711,18 +3464,21 @@
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="n">
-        <v>3</v>
-      </c>
-      <c r="G68" t="n">
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="n">
+        <v>3</v>
+      </c>
+      <c r="J68" t="n">
         <v>2.63</v>
       </c>
-      <c r="H68" t="n">
-        <v>3</v>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="n">
+        <v>3</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2735,14 +3491,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C69" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="D69" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E69" t="n">
-        <v>3</v>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2017-06-01</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2017-06-05</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>data_raw/jun-2017-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F69" t="n">
         <v>2.88</v>
@@ -2754,12 +3516,21 @@
         <v>3</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" t="inlineStr">
+        <v>2.5</v>
+      </c>
+      <c r="K69" t="n">
+        <v>3</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -2776,14 +3547,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C70" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="D70" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E70" t="n">
-        <v>3</v>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2017-07-13</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2017-07-17</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>data_raw/jul-2017-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F70" t="n">
         <v>2.75</v>
@@ -2795,12 +3572,21 @@
         <v>3</v>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="inlineStr">
+        <v>2.5</v>
+      </c>
+      <c r="K70" t="n">
+        <v>3</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -2816,18 +3602,21 @@
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="n">
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="n">
         <v>2.75</v>
       </c>
-      <c r="G71" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H71" t="n">
-        <v>3</v>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
+      <c r="J71" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K71" t="n">
+        <v>3</v>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2840,14 +3629,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C72" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="D72" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E72" t="n">
-        <v>3</v>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2017-09-07</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2017-09-11</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>data_raw/sep-2017-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F72" t="n">
         <v>2.75</v>
@@ -2859,12 +3654,21 @@
         <v>3</v>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" t="inlineStr">
+        <v>2.5</v>
+      </c>
+      <c r="K72" t="n">
+        <v>3</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -2881,14 +3685,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C73" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="D73" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E73" t="n">
-        <v>3</v>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2017-10-19</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2017-10-23</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>data_raw/oct-nov-2017-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F73" t="n">
         <v>2.75</v>
@@ -2900,12 +3710,21 @@
         <v>3</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" t="inlineStr">
+        <v>2.5</v>
+      </c>
+      <c r="K73" t="n">
+        <v>3</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -2921,18 +3740,21 @@
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="n">
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="n">
         <v>2.75</v>
       </c>
-      <c r="G74" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H74" t="n">
-        <v>3</v>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
+      <c r="J74" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K74" t="n">
+        <v>3</v>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2945,14 +3767,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C75" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="D75" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E75" t="n">
-        <v>3</v>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2017-11-30</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2017-12-04</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>data_raw/dec-2017-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F75" t="n">
         <v>2.75</v>
@@ -2964,12 +3792,21 @@
         <v>3</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" t="inlineStr">
+        <v>2.5</v>
+      </c>
+      <c r="K75" t="n">
+        <v>3</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -2986,14 +3823,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C76" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="D76" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E76" t="n">
-        <v>3</v>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2018-01-18</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2018-01-22</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>data_raw/jan-2018-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F76" t="n">
         <v>2.75</v>
@@ -3005,12 +3848,21 @@
         <v>3</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
-      </c>
-      <c r="K76" t="inlineStr">
+        <v>2.5</v>
+      </c>
+      <c r="K76" t="n">
+        <v>3</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -3026,18 +3878,21 @@
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="n">
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="n">
         <v>2.75</v>
       </c>
-      <c r="G77" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H77" t="n">
-        <v>3</v>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
+      <c r="J77" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K77" t="n">
+        <v>3</v>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3050,14 +3905,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C78" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="D78" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E78" t="n">
-        <v>3</v>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2018-03-08</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2018-03-12</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>data_raw/mar-2018-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F78" t="n">
         <v>2.75</v>
@@ -3069,12 +3930,21 @@
         <v>3</v>
       </c>
       <c r="I78" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="J78" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" t="inlineStr">
+        <v>2.5</v>
+      </c>
+      <c r="K78" t="n">
+        <v>3</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -3090,18 +3960,21 @@
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="n">
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="n">
         <v>2.75</v>
       </c>
-      <c r="G79" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H79" t="n">
-        <v>3</v>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
+      <c r="J79" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K79" t="n">
+        <v>3</v>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3114,14 +3987,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C80" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="D80" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E80" t="n">
-        <v>3</v>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2018-04-19</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2018-04-23</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>data_raw/may-2018-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F80" t="n">
         <v>2.75</v>
@@ -3133,12 +4012,21 @@
         <v>3</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" t="inlineStr">
+        <v>2.5</v>
+      </c>
+      <c r="K80" t="n">
+        <v>3</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -3155,14 +4043,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C81" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="D81" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E81" t="n">
-        <v>3</v>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2018-05-31</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2018-06-04</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>data_raw/jun-2018-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F81" t="n">
         <v>2.75</v>
@@ -3174,12 +4068,21 @@
         <v>3</v>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="J81" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" t="inlineStr">
+        <v>2.5</v>
+      </c>
+      <c r="K81" t="n">
+        <v>3</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -3196,14 +4099,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C82" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="D82" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E82" t="n">
-        <v>3</v>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2018-07-19</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2018-07-23</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>data_raw/jul-aug-2018-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F82" t="n">
         <v>2.75</v>
@@ -3215,12 +4124,21 @@
         <v>3</v>
       </c>
       <c r="I82" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
-      </c>
-      <c r="K82" t="inlineStr">
+        <v>2.5</v>
+      </c>
+      <c r="K82" t="n">
+        <v>3</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -3236,18 +4154,21 @@
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
-      <c r="F83" t="n">
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="n">
         <v>2.75</v>
       </c>
-      <c r="G83" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H83" t="n">
-        <v>3</v>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
+      <c r="J83" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K83" t="n">
+        <v>3</v>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3260,14 +4181,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C84" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="D84" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E84" t="n">
-        <v>3</v>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2018-09-13</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2018-09-17</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>data_raw/sep-2018-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F84" t="n">
         <v>2.75</v>
@@ -3279,12 +4206,21 @@
         <v>3</v>
       </c>
       <c r="I84" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="J84" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" t="inlineStr">
+        <v>2.5</v>
+      </c>
+      <c r="K84" t="n">
+        <v>3</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -3300,18 +4236,21 @@
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
-      <c r="F85" t="n">
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="n">
         <v>2.88</v>
       </c>
-      <c r="G85" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H85" t="n">
-        <v>3</v>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
+      <c r="J85" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K85" t="n">
+        <v>3</v>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3324,14 +4263,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C86" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="D86" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E86" t="n">
-        <v>3</v>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2018-10-25</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2018-10-29</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>data_raw/nov-2018-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F86" t="n">
         <v>2.88</v>
@@ -3343,12 +4288,21 @@
         <v>3</v>
       </c>
       <c r="I86" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="J86" t="n">
-        <v>0</v>
-      </c>
-      <c r="K86" t="inlineStr">
+        <v>2.5</v>
+      </c>
+      <c r="K86" t="n">
+        <v>3</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -3365,14 +4319,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C87" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="D87" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E87" t="n">
-        <v>3</v>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2018-12-06</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2018-12-10</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>data_raw/dec-2018-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F87" t="n">
         <v>2.88</v>
@@ -3384,12 +4344,21 @@
         <v>3</v>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="J87" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" t="inlineStr">
+        <v>2.5</v>
+      </c>
+      <c r="K87" t="n">
+        <v>3</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -3406,14 +4375,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C88" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="D88" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E88" t="n">
-        <v>3</v>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2019-01-17</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2019-01-22</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>data_raw/jan-2019-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F88" t="n">
         <v>2.75</v>
@@ -3425,12 +4400,21 @@
         <v>3</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" t="inlineStr">
+        <v>2.5</v>
+      </c>
+      <c r="K88" t="n">
+        <v>3</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -3446,18 +4430,21 @@
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
-      <c r="F89" t="n">
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="n">
         <v>2.75</v>
       </c>
-      <c r="G89" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H89" t="n">
-        <v>3</v>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
+      <c r="J89" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K89" t="n">
+        <v>3</v>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3470,14 +4457,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C90" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="D90" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E90" t="n">
-        <v>2.88</v>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2019-03-06</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2019-03-11</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>data_raw/mar-2019-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F90" t="n">
         <v>2.75</v>
@@ -3489,12 +4482,21 @@
         <v>2.88</v>
       </c>
       <c r="I90" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="J90" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" t="inlineStr">
+        <v>2.5</v>
+      </c>
+      <c r="K90" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -3510,18 +4512,21 @@
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
-      <c r="F91" t="n">
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="n">
         <v>2.75</v>
       </c>
-      <c r="G91" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H91" t="n">
+      <c r="J91" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K91" t="n">
         <v>2.88</v>
       </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3534,14 +4539,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C92" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="D92" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E92" t="n">
-        <v>2.88</v>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2019-04-17</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2019-04-22</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>data_raw/apr-may-2019-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F92" t="n">
         <v>2.75</v>
@@ -3553,12 +4564,21 @@
         <v>2.88</v>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" t="inlineStr">
+        <v>2.5</v>
+      </c>
+      <c r="K92" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -3575,14 +4595,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C93" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="D93" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E93" t="n">
-        <v>2.81</v>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2019-06-05</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2019-06-10</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>data_raw/jun-2019-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F93" t="n">
         <v>2.69</v>
@@ -3594,12 +4620,21 @@
         <v>2.81</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="J93" t="n">
-        <v>0</v>
-      </c>
-      <c r="K93" t="inlineStr">
+        <v>2.5</v>
+      </c>
+      <c r="K93" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -3616,14 +4651,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C94" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D94" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="E94" t="n">
-        <v>2.75</v>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2019-07-17</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2019-07-22</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>data_raw/jul-2019-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F94" t="n">
         <v>2.5</v>
@@ -3635,12 +4676,21 @@
         <v>2.75</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
-      </c>
-      <c r="K94" t="inlineStr">
+        <v>2.31</v>
+      </c>
+      <c r="K94" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -3656,18 +4706,21 @@
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
-      <c r="F95" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G95" t="n">
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J95" t="n">
         <v>2.31</v>
       </c>
-      <c r="H95" t="n">
+      <c r="K95" t="n">
         <v>2.75</v>
       </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3680,14 +4733,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C96" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D96" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="E96" t="n">
-        <v>2.56</v>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2019-09-04</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2019-09-09</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>data_raw/sep-2019-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F96" t="n">
         <v>2.5</v>
@@ -3699,12 +4758,21 @@
         <v>2.56</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="J96" t="n">
-        <v>0</v>
-      </c>
-      <c r="K96" t="inlineStr">
+        <v>2.25</v>
+      </c>
+      <c r="K96" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -3721,14 +4789,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C97" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D97" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="E97" t="n">
-        <v>2.56</v>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2019-10-16</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2019-10-21</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>data_raw/oct-2019-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F97" t="n">
         <v>2.5</v>
@@ -3740,12 +4814,21 @@
         <v>2.56</v>
       </c>
       <c r="I97" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="J97" t="n">
-        <v>0</v>
-      </c>
-      <c r="K97" t="inlineStr">
+        <v>2.25</v>
+      </c>
+      <c r="K97" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -3761,18 +4844,21 @@
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
-      <c r="F98" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G98" t="n">
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J98" t="n">
         <v>2.25</v>
       </c>
-      <c r="H98" t="n">
+      <c r="K98" t="n">
         <v>2.56</v>
       </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3785,14 +4871,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C99" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D99" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="E99" t="n">
-        <v>2.56</v>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2019-11-26</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2019-12-02</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>data_raw/dec-2019-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F99" t="n">
         <v>2.5</v>
@@ -3804,12 +4896,21 @@
         <v>2.56</v>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="J99" t="n">
-        <v>0</v>
-      </c>
-      <c r="K99" t="inlineStr">
+        <v>2.25</v>
+      </c>
+      <c r="K99" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -3826,14 +4927,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C100" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="D100" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="E100" t="n">
-        <v>2.56</v>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2020-01-15</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2020-01-21</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>data_raw/jan-2020-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F100" t="n">
         <v>2.4</v>
@@ -3845,12 +4952,21 @@
         <v>2.56</v>
       </c>
       <c r="I100" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="J100" t="n">
-        <v>0</v>
-      </c>
-      <c r="K100" t="inlineStr">
+        <v>2.25</v>
+      </c>
+      <c r="K100" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -3866,18 +4982,21 @@
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
-      <c r="F101" t="n">
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="n">
         <v>2.4</v>
       </c>
-      <c r="G101" t="n">
+      <c r="J101" t="n">
         <v>2.25</v>
       </c>
-      <c r="H101" t="n">
+      <c r="K101" t="n">
         <v>2.56</v>
       </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3890,14 +5009,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C102" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="D102" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="E102" t="n">
-        <v>2.56</v>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2020-03-04</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2020-03-09</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>data_raw/mar-2020-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F102" t="n">
         <v>2.25</v>
@@ -3909,12 +5034,21 @@
         <v>2.56</v>
       </c>
       <c r="I102" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="J102" t="n">
-        <v>0</v>
-      </c>
-      <c r="K102" t="inlineStr">
+        <v>2.06</v>
+      </c>
+      <c r="K102" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -3931,14 +5065,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C103" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="D103" t="n">
-        <v>2</v>
-      </c>
-      <c r="E103" t="n">
-        <v>2.5</v>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2020-04-15</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2020-04-20</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>data_raw/apr-2020-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F103" t="n">
         <v>2.19</v>
@@ -3950,12 +5090,21 @@
         <v>2.5</v>
       </c>
       <c r="I103" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="J103" t="n">
-        <v>0</v>
-      </c>
-      <c r="K103" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="K103" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -3971,18 +5120,21 @@
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr"/>
-      <c r="F104" t="n">
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="n">
         <v>2.19</v>
       </c>
-      <c r="G104" t="n">
+      <c r="J104" t="n">
         <v>2</v>
       </c>
-      <c r="H104" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3995,14 +5147,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C105" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="D105" t="n">
-        <v>2</v>
-      </c>
-      <c r="E105" t="n">
-        <v>2.5</v>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2020-05-27</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>data_raw/jun-2020-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F105" t="n">
         <v>2.25</v>
@@ -4014,12 +5172,21 @@
         <v>2.5</v>
       </c>
       <c r="I105" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="J105" t="n">
-        <v>0</v>
-      </c>
-      <c r="K105" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="K105" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -4036,14 +5203,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C106" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="D106" t="n">
-        <v>2</v>
-      </c>
-      <c r="E106" t="n">
-        <v>2.5</v>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2020-07-15</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2020-07-20</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>data_raw/jul-2020-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F106" t="n">
         <v>2.25</v>
@@ -4055,12 +5228,21 @@
         <v>2.5</v>
       </c>
       <c r="I106" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="J106" t="n">
-        <v>0</v>
-      </c>
-      <c r="K106" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="K106" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -4076,18 +5258,21 @@
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
-      <c r="F107" t="n">
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="n">
         <v>2.25</v>
       </c>
-      <c r="G107" t="n">
+      <c r="J107" t="n">
         <v>2</v>
       </c>
-      <c r="H107" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4100,14 +5285,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C108" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="D108" t="n">
-        <v>2</v>
-      </c>
-      <c r="E108" t="n">
-        <v>2.5</v>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2020-09-02</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2020-09-08</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>data_raw/sep-2020-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F108" t="n">
         <v>2.25</v>
@@ -4119,12 +5310,21 @@
         <v>2.5</v>
       </c>
       <c r="I108" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="J108" t="n">
-        <v>0</v>
-      </c>
-      <c r="K108" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="K108" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -4140,18 +5340,21 @@
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
-      <c r="F109" t="n">
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="n">
         <v>2.25</v>
       </c>
-      <c r="G109" t="n">
+      <c r="J109" t="n">
         <v>2</v>
       </c>
-      <c r="H109" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4164,14 +5367,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C110" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="D110" t="n">
-        <v>2</v>
-      </c>
-      <c r="E110" t="n">
-        <v>2.5</v>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2020-10-21</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2020-10-26</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>data_raw/nov-2020-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F110" t="n">
         <v>2.25</v>
@@ -4183,12 +5392,21 @@
         <v>2.5</v>
       </c>
       <c r="I110" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="J110" t="n">
-        <v>0</v>
-      </c>
-      <c r="K110" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="K110" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" t="n">
+        <v>0</v>
+      </c>
+      <c r="N110" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -4205,14 +5423,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C111" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="D111" t="n">
-        <v>2</v>
-      </c>
-      <c r="E111" t="n">
-        <v>2.5</v>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2020-12-02</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2020-12-07</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>data_raw/dec-2020-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F111" t="n">
         <v>2.25</v>
@@ -4224,12 +5448,21 @@
         <v>2.5</v>
       </c>
       <c r="I111" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="J111" t="n">
-        <v>0</v>
-      </c>
-      <c r="K111" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="K111" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0</v>
+      </c>
+      <c r="N111" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -4246,14 +5479,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C112" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="D112" t="n">
-        <v>2</v>
-      </c>
-      <c r="E112" t="n">
-        <v>2.5</v>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2021-01-13</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2021-01-19</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>data_raw/jan-2021-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F112" t="n">
         <v>2.25</v>
@@ -4265,12 +5504,21 @@
         <v>2.5</v>
       </c>
       <c r="I112" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="J112" t="n">
-        <v>0</v>
-      </c>
-      <c r="K112" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="K112" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0</v>
+      </c>
+      <c r="N112" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -4286,18 +5534,21 @@
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr"/>
-      <c r="F113" t="n">
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="n">
         <v>2.25</v>
       </c>
-      <c r="G113" t="n">
+      <c r="J113" t="n">
         <v>2</v>
       </c>
-      <c r="H113" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4310,17 +5561,23 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C114" t="n">
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2021-03-03</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2021-03-08</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>data_raw/mar-2021-spd-results.pdf</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
         <v>2.25</v>
-      </c>
-      <c r="D114" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="E114" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F114" t="n">
-        <v>2.31</v>
       </c>
       <c r="G114" t="n">
         <v>2.13</v>
@@ -4329,12 +5586,21 @@
         <v>2.5</v>
       </c>
       <c r="I114" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="J114" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="K114" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L114" t="n">
         <v>-0.06000000000000005</v>
       </c>
-      <c r="J114" t="n">
+      <c r="M114" t="n">
         <v>0.06000000000000005</v>
       </c>
-      <c r="K114" t="inlineStr">
+      <c r="N114" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -4351,14 +5617,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C115" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="D115" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="E115" t="n">
-        <v>2.5</v>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>2021-04-14</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2021-04-19</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>data_raw/apr-2021-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F115" t="n">
         <v>2.31</v>
@@ -4370,12 +5642,21 @@
         <v>2.5</v>
       </c>
       <c r="I115" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="J115" t="n">
-        <v>0</v>
-      </c>
-      <c r="K115" t="inlineStr">
+        <v>2.13</v>
+      </c>
+      <c r="K115" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L115" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0</v>
+      </c>
+      <c r="N115" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -4391,18 +5672,21 @@
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
-      <c r="F116" t="n">
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="n">
         <v>2.31</v>
       </c>
-      <c r="G116" t="n">
+      <c r="J116" t="n">
         <v>2.13</v>
       </c>
-      <c r="H116" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4415,14 +5699,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C117" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="D117" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="E117" t="n">
-        <v>2.5</v>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2021-06-02</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2021-06-07</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>data_raw/jun-2021-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F117" t="n">
         <v>2.31</v>
@@ -4434,12 +5724,21 @@
         <v>2.5</v>
       </c>
       <c r="I117" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="J117" t="n">
-        <v>0</v>
-      </c>
-      <c r="K117" t="inlineStr">
+        <v>2.06</v>
+      </c>
+      <c r="K117" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0</v>
+      </c>
+      <c r="N117" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -4456,14 +5755,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C118" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="D118" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="E118" t="n">
-        <v>2.5</v>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2021-07-14</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2021-07-19</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>data_raw/jul-2021-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F118" t="n">
         <v>2.25</v>
@@ -4475,12 +5780,21 @@
         <v>2.5</v>
       </c>
       <c r="I118" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="J118" t="n">
-        <v>0</v>
-      </c>
-      <c r="K118" t="inlineStr">
+        <v>2.06</v>
+      </c>
+      <c r="K118" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0</v>
+      </c>
+      <c r="N118" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -4496,18 +5810,21 @@
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
-      <c r="F119" t="n">
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="n">
         <v>2.25</v>
       </c>
-      <c r="G119" t="n">
+      <c r="J119" t="n">
         <v>2.06</v>
       </c>
-      <c r="H119" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4520,14 +5837,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C120" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="D120" t="n">
-        <v>2</v>
-      </c>
-      <c r="E120" t="n">
-        <v>2.5</v>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2021-09-13</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>data_raw/sep-2021-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F120" t="n">
         <v>2.25</v>
@@ -4539,12 +5862,21 @@
         <v>2.5</v>
       </c>
       <c r="I120" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="J120" t="n">
-        <v>0</v>
-      </c>
-      <c r="K120" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="K120" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -4560,18 +5892,21 @@
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
-      <c r="F121" t="n">
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="n">
         <v>2.25</v>
       </c>
-      <c r="G121" t="n">
+      <c r="J121" t="n">
         <v>2</v>
       </c>
-      <c r="H121" t="n">
+      <c r="K121" t="n">
         <v>2.44</v>
       </c>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4584,14 +5919,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C122" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="D122" t="n">
-        <v>2</v>
-      </c>
-      <c r="E122" t="n">
-        <v>2.44</v>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2021-10-20</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2021-10-25</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>data_raw/nov-2021-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F122" t="n">
         <v>2.25</v>
@@ -4603,12 +5944,21 @@
         <v>2.44</v>
       </c>
       <c r="I122" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="J122" t="n">
-        <v>0</v>
-      </c>
-      <c r="K122" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="K122" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -4625,14 +5975,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C123" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="D123" t="n">
-        <v>2</v>
-      </c>
-      <c r="E123" t="n">
-        <v>2.44</v>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2021-12-01</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2021-12-06</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>data_raw/dec-2021-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F123" t="n">
         <v>2.25</v>
@@ -4644,12 +6000,21 @@
         <v>2.44</v>
       </c>
       <c r="I123" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="J123" t="n">
-        <v>0</v>
-      </c>
-      <c r="K123" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="K123" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -4666,14 +6031,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C124" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="D124" t="n">
-        <v>2</v>
-      </c>
-      <c r="E124" t="n">
-        <v>2.44</v>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>2022-01-12</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2022-01-18</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>data_raw/jan-2022-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F124" t="n">
         <v>2.25</v>
@@ -4685,12 +6056,21 @@
         <v>2.44</v>
       </c>
       <c r="I124" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="J124" t="n">
-        <v>0</v>
-      </c>
-      <c r="K124" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="K124" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0</v>
+      </c>
+      <c r="N124" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -4706,18 +6086,21 @@
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr"/>
-      <c r="F125" t="n">
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="n">
         <v>2.25</v>
       </c>
-      <c r="G125" t="n">
+      <c r="J125" t="n">
         <v>2</v>
       </c>
-      <c r="H125" t="n">
+      <c r="K125" t="n">
         <v>2.44</v>
       </c>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4730,14 +6113,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C126" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="D126" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="E126" t="n">
-        <v>2.5</v>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>2022-03-02</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2022-03-07</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>data_raw/mar-2022-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F126" t="n">
         <v>2.25</v>
@@ -4749,12 +6138,21 @@
         <v>2.5</v>
       </c>
       <c r="I126" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="J126" t="n">
-        <v>0</v>
-      </c>
-      <c r="K126" t="inlineStr">
+        <v>2.13</v>
+      </c>
+      <c r="K126" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -4770,18 +6168,21 @@
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr"/>
-      <c r="F127" t="n">
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="n">
         <v>2.38</v>
       </c>
-      <c r="G127" t="n">
+      <c r="J127" t="n">
         <v>2.13</v>
       </c>
-      <c r="H127" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4794,14 +6195,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C128" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="D128" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="E128" t="n">
-        <v>2.5</v>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>2022-04-20</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2022-04-25</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>data_raw/may-2022-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F128" t="n">
         <v>2.38</v>
@@ -4813,12 +6220,21 @@
         <v>2.5</v>
       </c>
       <c r="I128" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="J128" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="K128" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L128" t="n">
         <v>-4.440892098500626e-16</v>
       </c>
-      <c r="J128" t="n">
+      <c r="M128" t="n">
         <v>4.440892098500626e-16</v>
       </c>
-      <c r="K128" t="inlineStr">
+      <c r="N128" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -4835,14 +6251,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C129" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="D129" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="E129" t="n">
-        <v>2.5</v>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>2022-06-01</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2022-06-06</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>data_raw/jun-2022-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F129" t="n">
         <v>2.38</v>
@@ -4854,12 +6276,21 @@
         <v>2.5</v>
       </c>
       <c r="I129" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="J129" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="K129" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L129" t="n">
         <v>-4.440892098500626e-16</v>
       </c>
-      <c r="J129" t="n">
+      <c r="M129" t="n">
         <v>4.440892098500626e-16</v>
       </c>
-      <c r="K129" t="inlineStr">
+      <c r="N129" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -4876,14 +6307,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C130" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="D130" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="E130" t="n">
-        <v>2.5</v>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>2022-07-13</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2022-07-18</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>data_raw/jul-2022-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F130" t="n">
         <v>2.38</v>
@@ -4895,12 +6332,21 @@
         <v>2.5</v>
       </c>
       <c r="I130" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="J130" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="K130" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L130" t="n">
         <v>-4.440892098500626e-16</v>
       </c>
-      <c r="J130" t="n">
+      <c r="M130" t="n">
         <v>4.440892098500626e-16</v>
       </c>
-      <c r="K130" t="inlineStr">
+      <c r="N130" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -4916,18 +6362,21 @@
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr"/>
-      <c r="F131" t="n">
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="n">
         <v>2.38</v>
       </c>
-      <c r="G131" t="n">
+      <c r="J131" t="n">
         <v>2.13</v>
       </c>
-      <c r="H131" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4940,14 +6389,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C132" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="D132" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="E132" t="n">
-        <v>2.5</v>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>2022-09-07</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2022-09-12</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>data_raw/sep-2022-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F132" t="n">
         <v>2.38</v>
@@ -4959,12 +6414,21 @@
         <v>2.5</v>
       </c>
       <c r="I132" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="J132" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="K132" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L132" t="n">
         <v>-4.440892098500626e-16</v>
       </c>
-      <c r="J132" t="n">
+      <c r="M132" t="n">
         <v>4.440892098500626e-16</v>
       </c>
-      <c r="K132" t="inlineStr">
+      <c r="N132" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -4980,18 +6444,21 @@
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr"/>
-      <c r="F133" t="n">
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="n">
         <v>2.4</v>
       </c>
-      <c r="G133" t="n">
+      <c r="J133" t="n">
         <v>2.25</v>
       </c>
-      <c r="H133" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5004,14 +6471,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C134" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="D134" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="E134" t="n">
-        <v>2.5</v>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>2022-10-19</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2022-10-24</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>data_raw/nov-2022-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F134" t="n">
         <v>2.4</v>
@@ -5023,12 +6496,21 @@
         <v>2.5</v>
       </c>
       <c r="I134" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="J134" t="n">
-        <v>0</v>
-      </c>
-      <c r="K134" t="inlineStr">
+        <v>2.25</v>
+      </c>
+      <c r="K134" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0</v>
+      </c>
+      <c r="N134" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -5045,14 +6527,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C135" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D135" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="E135" t="n">
-        <v>2.5</v>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>2022-11-30</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2022-12-05</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>data_raw/dec-2022-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F135" t="n">
         <v>2.5</v>
@@ -5064,12 +6552,21 @@
         <v>2.5</v>
       </c>
       <c r="I135" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="J135" t="n">
-        <v>0</v>
-      </c>
-      <c r="K135" t="inlineStr">
+        <v>2.25</v>
+      </c>
+      <c r="K135" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0</v>
+      </c>
+      <c r="N135" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -5086,14 +6583,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C136" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D136" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="E136" t="n">
-        <v>2.5</v>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>2023-01-18</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2023-01-23</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>data_raw/jan-feb-2023-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F136" t="n">
         <v>2.5</v>
@@ -5105,12 +6608,21 @@
         <v>2.5</v>
       </c>
       <c r="I136" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="J136" t="n">
-        <v>0</v>
-      </c>
-      <c r="K136" t="inlineStr">
+        <v>2.25</v>
+      </c>
+      <c r="K136" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N136" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -5126,18 +6638,21 @@
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr"/>
-      <c r="F137" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G137" t="n">
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J137" t="n">
         <v>2.25</v>
       </c>
-      <c r="H137" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5150,14 +6665,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C138" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D138" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="E138" t="n">
-        <v>2.63</v>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>2023-03-08</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2023-03-14</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>data_raw/mar-2023-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F138" t="n">
         <v>2.5</v>
@@ -5169,12 +6690,21 @@
         <v>2.63</v>
       </c>
       <c r="I138" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="J138" t="n">
-        <v>0</v>
-      </c>
-      <c r="K138" t="inlineStr">
+        <v>2.38</v>
+      </c>
+      <c r="K138" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -5190,18 +6720,21 @@
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
-      <c r="F139" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G139" t="n">
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J139" t="n">
         <v>2.4</v>
       </c>
-      <c r="H139" t="n">
+      <c r="K139" t="n">
         <v>2.63</v>
       </c>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5214,14 +6747,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C140" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D140" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="E140" t="n">
-        <v>2.63</v>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2023-04-24</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>data_raw/may-2023-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F140" t="n">
         <v>2.5</v>
@@ -5233,12 +6772,21 @@
         <v>2.63</v>
       </c>
       <c r="I140" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="J140" t="n">
-        <v>0</v>
-      </c>
-      <c r="K140" t="inlineStr">
+        <v>2.4</v>
+      </c>
+      <c r="K140" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0</v>
+      </c>
+      <c r="N140" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -5255,14 +6803,20 @@
           <t>SPD</t>
         </is>
       </c>
-      <c r="C141" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D141" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E141" t="n">
-        <v>2.63</v>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2023-05-31</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2023-06-05</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>data_raw/jun-2023-spd-results.pdf</t>
+        </is>
       </c>
       <c r="F141" t="n">
         <v>2.5</v>
@@ -5274,12 +6828,21 @@
         <v>2.63</v>
       </c>
       <c r="I141" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="J141" t="n">
-        <v>0</v>
-      </c>
-      <c r="K141" t="inlineStr">
+        <v>2.5</v>
+      </c>
+      <c r="K141" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0</v>
+      </c>
+      <c r="N141" t="inlineStr">
         <is>
           <t>pdf_llm</t>
         </is>
@@ -5296,14 +6859,20 @@
           <t>Combined</t>
         </is>
       </c>
-      <c r="C142" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D142" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="E142" t="n">
-        <v>2.75</v>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2023-07-12</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>data_raw/jul-2023-smp-results.pdf</t>
+        </is>
       </c>
       <c r="F142" t="n">
         <v>2.5</v>
@@ -5315,12 +6884,21 @@
         <v>2.75</v>
       </c>
       <c r="I142" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="J142" t="n">
-        <v>0</v>
-      </c>
-      <c r="K142" t="inlineStr">
+        <v>2.38</v>
+      </c>
+      <c r="K142" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0</v>
+      </c>
+      <c r="N142" t="inlineStr">
         <is>
           <t>xlsx</t>
         </is>
@@ -5336,18 +6914,21 @@
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
-      <c r="F143" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G143" t="n">
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J143" t="n">
         <v>2.38</v>
       </c>
-      <c r="H143" t="n">
+      <c r="K143" t="n">
         <v>2.75</v>
       </c>
-      <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5360,14 +6941,20 @@
           <t>Combined</t>
         </is>
       </c>
-      <c r="C144" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="D144" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E144" t="n">
-        <v>2.88</v>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>data_raw/sep-2023-smp-results.pdf</t>
+        </is>
       </c>
       <c r="F144" t="n">
         <v>2.56</v>
@@ -5379,12 +6966,21 @@
         <v>2.88</v>
       </c>
       <c r="I144" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="J144" t="n">
-        <v>0</v>
-      </c>
-      <c r="K144" t="inlineStr">
+        <v>2.5</v>
+      </c>
+      <c r="K144" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="L144" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" t="n">
+        <v>0</v>
+      </c>
+      <c r="N144" t="inlineStr">
         <is>
           <t>xlsx</t>
         </is>
@@ -5401,14 +6997,20 @@
           <t>Combined</t>
         </is>
       </c>
-      <c r="C145" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="D145" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E145" t="n">
-        <v>3</v>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>data_raw/oct-2023-smp-results.pdf</t>
+        </is>
       </c>
       <c r="F145" t="n">
         <v>2.63</v>
@@ -5420,12 +7022,21 @@
         <v>3</v>
       </c>
       <c r="I145" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="J145" t="n">
-        <v>0</v>
-      </c>
-      <c r="K145" t="inlineStr">
+        <v>2.5</v>
+      </c>
+      <c r="K145" t="n">
+        <v>3</v>
+      </c>
+      <c r="L145" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" t="n">
+        <v>0</v>
+      </c>
+      <c r="N145" t="inlineStr">
         <is>
           <t>xlsx</t>
         </is>
@@ -5441,18 +7052,21 @@
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
-      <c r="F146" t="n">
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="n">
         <v>2.63</v>
       </c>
-      <c r="G146" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H146" t="n">
-        <v>3</v>
-      </c>
-      <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
+      <c r="J146" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K146" t="n">
+        <v>3</v>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5465,14 +7079,20 @@
           <t>Combined</t>
         </is>
       </c>
-      <c r="C147" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="D147" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E147" t="n">
-        <v>3</v>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2023-12-04</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>data_raw/dec-2023-smp-results.pdf</t>
+        </is>
       </c>
       <c r="F147" t="n">
         <v>2.75</v>
@@ -5484,12 +7104,21 @@
         <v>3</v>
       </c>
       <c r="I147" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="J147" t="n">
-        <v>0</v>
-      </c>
-      <c r="K147" t="inlineStr">
+        <v>2.5</v>
+      </c>
+      <c r="K147" t="n">
+        <v>3</v>
+      </c>
+      <c r="L147" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" t="n">
+        <v>0</v>
+      </c>
+      <c r="N147" t="inlineStr">
         <is>
           <t>xlsx</t>
         </is>
@@ -5506,14 +7135,20 @@
           <t>Combined</t>
         </is>
       </c>
-      <c r="C148" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="D148" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E148" t="n">
-        <v>3.08</v>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2024-01-17</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2024-01-22</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>data_raw/jan-2024-smp-results.pdf</t>
+        </is>
       </c>
       <c r="F148" t="n">
         <v>2.75</v>
@@ -5525,12 +7160,21 @@
         <v>3.08</v>
       </c>
       <c r="I148" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="J148" t="n">
-        <v>0</v>
-      </c>
-      <c r="K148" t="inlineStr">
+        <v>2.5</v>
+      </c>
+      <c r="K148" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="L148" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" t="n">
+        <v>0</v>
+      </c>
+      <c r="N148" t="inlineStr">
         <is>
           <t>xlsx</t>
         </is>
@@ -5546,18 +7190,21 @@
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr"/>
-      <c r="F149" t="n">
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="n">
         <v>2.75</v>
       </c>
-      <c r="G149" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H149" t="n">
+      <c r="J149" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K149" t="n">
         <v>3.08</v>
       </c>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5570,14 +7217,20 @@
           <t>Combined</t>
         </is>
       </c>
-      <c r="C150" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="D150" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E150" t="n">
-        <v>3.11</v>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>data_raw/mar-2024-smp-results.pdf</t>
+        </is>
       </c>
       <c r="F150" t="n">
         <v>2.75</v>
@@ -5589,12 +7242,21 @@
         <v>3.11</v>
       </c>
       <c r="I150" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="J150" t="n">
-        <v>0</v>
-      </c>
-      <c r="K150" t="inlineStr">
+        <v>2.5</v>
+      </c>
+      <c r="K150" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="L150" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" t="n">
+        <v>0</v>
+      </c>
+      <c r="N150" t="inlineStr">
         <is>
           <t>xlsx</t>
         </is>
@@ -5610,18 +7272,21 @@
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr"/>
-      <c r="F151" t="n">
-        <v>3</v>
-      </c>
-      <c r="G151" t="n">
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="n">
+        <v>3</v>
+      </c>
+      <c r="J151" t="n">
         <v>2.63</v>
       </c>
-      <c r="H151" t="n">
+      <c r="K151" t="n">
         <v>3.13</v>
       </c>
-      <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5634,14 +7299,20 @@
           <t>Combined</t>
         </is>
       </c>
-      <c r="C152" t="n">
-        <v>3</v>
-      </c>
-      <c r="D152" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="E152" t="n">
-        <v>3.13</v>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2024-04-22</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>data_raw/apr-may-2024-smp-results.pdf</t>
+        </is>
       </c>
       <c r="F152" t="n">
         <v>3</v>
@@ -5653,12 +7324,21 @@
         <v>3.13</v>
       </c>
       <c r="I152" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J152" t="n">
-        <v>0</v>
-      </c>
-      <c r="K152" t="inlineStr">
+        <v>2.63</v>
+      </c>
+      <c r="K152" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="L152" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" t="n">
+        <v>0</v>
+      </c>
+      <c r="N152" t="inlineStr">
         <is>
           <t>xlsx</t>
         </is>
@@ -5675,14 +7355,20 @@
           <t>Combined</t>
         </is>
       </c>
-      <c r="C153" t="n">
-        <v>3</v>
-      </c>
-      <c r="D153" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="E153" t="n">
-        <v>3.13</v>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2024-06-03</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>data_raw/jun-2024-smp-results.pdf</t>
+        </is>
       </c>
       <c r="F153" t="n">
         <v>3</v>
@@ -5694,12 +7380,21 @@
         <v>3.13</v>
       </c>
       <c r="I153" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J153" t="n">
-        <v>0</v>
-      </c>
-      <c r="K153" t="inlineStr">
+        <v>2.72</v>
+      </c>
+      <c r="K153" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="L153" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" t="n">
+        <v>0</v>
+      </c>
+      <c r="N153" t="inlineStr">
         <is>
           <t>xlsx</t>
         </is>
@@ -5716,14 +7411,20 @@
           <t>Combined</t>
         </is>
       </c>
-      <c r="C154" t="n">
-        <v>3</v>
-      </c>
-      <c r="D154" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="E154" t="n">
-        <v>3.25</v>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>2024-07-17</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>data_raw/jul-2024-smp-results.pdf</t>
+        </is>
       </c>
       <c r="F154" t="n">
         <v>3</v>
@@ -5735,12 +7436,21 @@
         <v>3.25</v>
       </c>
       <c r="I154" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J154" t="n">
-        <v>0</v>
-      </c>
-      <c r="K154" t="inlineStr">
+        <v>2.75</v>
+      </c>
+      <c r="K154" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L154" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" t="n">
+        <v>0</v>
+      </c>
+      <c r="N154" t="inlineStr">
         <is>
           <t>xlsx</t>
         </is>
@@ -5756,18 +7466,21 @@
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr"/>
-      <c r="F155" t="n">
-        <v>3</v>
-      </c>
-      <c r="G155" t="n">
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="n">
+        <v>3</v>
+      </c>
+      <c r="J155" t="n">
         <v>2.75</v>
       </c>
-      <c r="H155" t="n">
+      <c r="K155" t="n">
         <v>3.25</v>
       </c>
-      <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5780,14 +7493,20 @@
           <t>Combined</t>
         </is>
       </c>
-      <c r="C156" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="D156" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="E156" t="n">
-        <v>3.13</v>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>data_raw/sep-2024-smp-results.pdf</t>
+        </is>
       </c>
       <c r="F156" t="n">
         <v>2.88</v>
@@ -5799,12 +7518,21 @@
         <v>3.13</v>
       </c>
       <c r="I156" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="J156" t="n">
-        <v>0</v>
-      </c>
-      <c r="K156" t="inlineStr">
+        <v>2.75</v>
+      </c>
+      <c r="K156" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="L156" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" t="n">
+        <v>0</v>
+      </c>
+      <c r="N156" t="inlineStr">
         <is>
           <t>xlsx</t>
         </is>
@@ -5820,18 +7548,21 @@
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr"/>
-      <c r="F157" t="n">
-        <v>3</v>
-      </c>
-      <c r="G157" t="n">
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="n">
+        <v>3</v>
+      </c>
+      <c r="J157" t="n">
         <v>2.75</v>
       </c>
-      <c r="H157" t="n">
+      <c r="K157" t="n">
         <v>3.13</v>
       </c>
-      <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5844,14 +7575,20 @@
           <t>Combined</t>
         </is>
       </c>
-      <c r="C158" t="n">
-        <v>3</v>
-      </c>
-      <c r="D158" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="E158" t="n">
-        <v>3.13</v>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>data_raw/nov-2024-smp-results.pdf</t>
+        </is>
       </c>
       <c r="F158" t="n">
         <v>3</v>
@@ -5863,12 +7600,21 @@
         <v>3.13</v>
       </c>
       <c r="I158" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J158" t="n">
-        <v>0</v>
-      </c>
-      <c r="K158" t="inlineStr">
+        <v>2.75</v>
+      </c>
+      <c r="K158" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="L158" t="n">
+        <v>0</v>
+      </c>
+      <c r="M158" t="n">
+        <v>0</v>
+      </c>
+      <c r="N158" t="inlineStr">
         <is>
           <t>xlsx</t>
         </is>
@@ -5885,31 +7631,46 @@
           <t>Combined</t>
         </is>
       </c>
-      <c r="C159" t="n">
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>data_raw/dec-2024-smp-results.pdf</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
         <v>3.13</v>
       </c>
-      <c r="D159" t="n">
+      <c r="G159" t="n">
         <v>2.88</v>
       </c>
-      <c r="E159" t="n">
+      <c r="H159" t="n">
         <v>3.38</v>
       </c>
-      <c r="F159" t="n">
-        <v>3</v>
-      </c>
-      <c r="G159" t="n">
+      <c r="I159" t="n">
+        <v>3</v>
+      </c>
+      <c r="J159" t="n">
         <v>2.72</v>
       </c>
-      <c r="H159" t="n">
+      <c r="K159" t="n">
         <v>3.19</v>
       </c>
-      <c r="I159" t="n">
+      <c r="L159" t="n">
         <v>0.1299999999999999</v>
       </c>
-      <c r="J159" t="n">
+      <c r="M159" t="n">
         <v>0.1299999999999999</v>
       </c>
-      <c r="K159" t="inlineStr">
+      <c r="N159" t="inlineStr">
         <is>
           <t>xlsx</t>
         </is>
@@ -5926,14 +7687,20 @@
           <t>Combined</t>
         </is>
       </c>
-      <c r="C160" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="D160" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="E160" t="n">
-        <v>3.45</v>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2025-01-21</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>data_raw/jan-2025-sme-results.pdf</t>
+        </is>
       </c>
       <c r="F160" t="n">
         <v>3.13</v>
@@ -5945,12 +7712,21 @@
         <v>3.45</v>
       </c>
       <c r="I160" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="J160" t="n">
-        <v>0</v>
-      </c>
-      <c r="K160" t="inlineStr">
+        <v>2.88</v>
+      </c>
+      <c r="K160" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L160" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" t="n">
+        <v>0</v>
+      </c>
+      <c r="N160" t="inlineStr">
         <is>
           <t>xlsx</t>
         </is>
@@ -5966,18 +7742,21 @@
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr"/>
-      <c r="F161" t="n">
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="n">
         <v>3.13</v>
       </c>
-      <c r="G161" t="n">
+      <c r="J161" t="n">
         <v>2.88</v>
       </c>
-      <c r="H161" t="n">
+      <c r="K161" t="n">
         <v>3.45</v>
       </c>
-      <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5990,14 +7769,20 @@
           <t>Combined</t>
         </is>
       </c>
-      <c r="C162" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="D162" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="E162" t="n">
-        <v>3.4</v>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>data_raw/mar-2025-sme-results.pdf</t>
+        </is>
       </c>
       <c r="F162" t="n">
         <v>3.13</v>
@@ -6009,12 +7794,21 @@
         <v>3.4</v>
       </c>
       <c r="I162" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="J162" t="n">
-        <v>0</v>
-      </c>
-      <c r="K162" t="inlineStr">
+        <v>2.88</v>
+      </c>
+      <c r="K162" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L162" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" t="n">
+        <v>0</v>
+      </c>
+      <c r="N162" t="inlineStr">
         <is>
           <t>xlsx</t>
         </is>
@@ -6030,18 +7824,21 @@
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr"/>
-      <c r="F163" t="n">
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="n">
         <v>3.13</v>
       </c>
-      <c r="G163" t="n">
+      <c r="J163" t="n">
         <v>2.88</v>
       </c>
-      <c r="H163" t="n">
+      <c r="K163" t="n">
         <v>3.8</v>
       </c>
-      <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6054,14 +7851,20 @@
           <t>Combined</t>
         </is>
       </c>
-      <c r="C164" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="D164" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="E164" t="n">
-        <v>3.38</v>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2025-04-28</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>data_raw/may-2025-sme-results.pdf</t>
+        </is>
       </c>
       <c r="F164" t="n">
         <v>3.13</v>
@@ -6070,15 +7873,24 @@
         <v>2.88</v>
       </c>
       <c r="H164" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="I164" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="J164" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K164" t="n">
         <v>3.8</v>
       </c>
-      <c r="I164" t="n">
-        <v>0</v>
-      </c>
-      <c r="J164" t="n">
-        <v>0</v>
-      </c>
-      <c r="K164" t="inlineStr">
+      <c r="L164" t="n">
+        <v>0</v>
+      </c>
+      <c r="M164" t="n">
+        <v>0</v>
+      </c>
+      <c r="N164" t="inlineStr">
         <is>
           <t>xlsx</t>
         </is>
@@ -6095,14 +7907,20 @@
           <t>Combined</t>
         </is>
       </c>
-      <c r="C165" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="D165" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="E165" t="n">
-        <v>3.39</v>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>data_raw/jun-2025-sme-results.pdf</t>
+        </is>
       </c>
       <c r="F165" t="n">
         <v>3.13</v>
@@ -6114,12 +7932,21 @@
         <v>3.39</v>
       </c>
       <c r="I165" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="J165" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="K165" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="L165" t="n">
         <v>-4.440892098500626e-16</v>
       </c>
-      <c r="J165" t="n">
+      <c r="M165" t="n">
         <v>4.440892098500626e-16</v>
       </c>
-      <c r="K165" t="inlineStr">
+      <c r="N165" t="inlineStr">
         <is>
           <t>xlsx</t>
         </is>
@@ -6136,14 +7963,20 @@
           <t>Combined</t>
         </is>
       </c>
-      <c r="C166" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="D166" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="E166" t="n">
-        <v>3.38</v>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>data_raw/jul-2025-sme-results.pdf</t>
+        </is>
       </c>
       <c r="F166" t="n">
         <v>3.13</v>
@@ -6155,12 +7988,21 @@
         <v>3.38</v>
       </c>
       <c r="I166" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="J166" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K166" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="L166" t="n">
         <v>-4.440892098500626e-16</v>
       </c>
-      <c r="J166" t="n">
+      <c r="M166" t="n">
         <v>4.440892098500626e-16</v>
       </c>
-      <c r="K166" t="inlineStr">
+      <c r="N166" t="inlineStr">
         <is>
           <t>xlsx</t>
         </is>
@@ -6176,18 +8018,21 @@
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr"/>
-      <c r="F167" t="n">
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="n">
         <v>3.13</v>
       </c>
-      <c r="G167" t="n">
+      <c r="J167" t="n">
         <v>2.88</v>
       </c>
-      <c r="H167" t="n">
+      <c r="K167" t="n">
         <v>3.38</v>
       </c>
-      <c r="I167" t="inlineStr"/>
-      <c r="J167" t="inlineStr"/>
-      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -6200,14 +8045,20 @@
           <t>Combined</t>
         </is>
       </c>
-      <c r="C168" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="D168" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="E168" t="n">
-        <v>3.38</v>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>data_raw/sep-2025-sme-results.pdf</t>
+        </is>
       </c>
       <c r="F168" t="n">
         <v>3.13</v>
@@ -6219,12 +8070,21 @@
         <v>3.38</v>
       </c>
       <c r="I168" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="J168" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K168" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="L168" t="n">
         <v>-4.440892098500626e-16</v>
       </c>
-      <c r="J168" t="n">
+      <c r="M168" t="n">
         <v>4.440892098500626e-16</v>
       </c>
-      <c r="K168" t="inlineStr">
+      <c r="N168" t="inlineStr">
         <is>
           <t>xlsx</t>
         </is>
@@ -6241,14 +8101,20 @@
           <t>Combined</t>
         </is>
       </c>
-      <c r="C169" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="D169" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="E169" t="n">
-        <v>3.38</v>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>data_raw/oct-2025-sme-results.pdf</t>
+        </is>
       </c>
       <c r="F169" t="n">
         <v>3.13</v>
@@ -6260,12 +8126,21 @@
         <v>3.38</v>
       </c>
       <c r="I169" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="J169" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K169" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="L169" t="n">
         <v>-4.440892098500626e-16</v>
       </c>
-      <c r="J169" t="n">
+      <c r="M169" t="n">
         <v>4.440892098500626e-16</v>
       </c>
-      <c r="K169" t="inlineStr">
+      <c r="N169" t="inlineStr">
         <is>
           <t>xlsx</t>
         </is>
@@ -6281,18 +8156,21 @@
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr"/>
-      <c r="F170" t="n">
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="n">
         <v>3.13</v>
       </c>
-      <c r="G170" t="n">
+      <c r="J170" t="n">
         <v>2.88</v>
       </c>
-      <c r="H170" t="n">
+      <c r="K170" t="n">
         <v>3.38</v>
       </c>
-      <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -6305,14 +8183,20 @@
           <t>Combined</t>
         </is>
       </c>
-      <c r="C171" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="D171" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="E171" t="n">
-        <v>3.38</v>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>data_raw/dec-2025-sme-results.pdf</t>
+        </is>
       </c>
       <c r="F171" t="n">
         <v>3.13</v>
@@ -6324,12 +8208,21 @@
         <v>3.38</v>
       </c>
       <c r="I171" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="J171" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K171" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="L171" t="n">
         <v>-4.440892098500626e-16</v>
       </c>
-      <c r="J171" t="n">
+      <c r="M171" t="n">
         <v>4.440892098500626e-16</v>
       </c>
-      <c r="K171" t="inlineStr">
+      <c r="N171" t="inlineStr">
         <is>
           <t>xlsx</t>
         </is>
@@ -6346,21 +8239,36 @@
           <t>Combined</t>
         </is>
       </c>
-      <c r="C172" t="n">
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>data_raw/jan-2026-sme-results.pdf</t>
+        </is>
+      </c>
+      <c r="F172" t="n">
         <v>3.1</v>
       </c>
-      <c r="D172" t="n">
-        <v>3</v>
-      </c>
-      <c r="E172" t="n">
+      <c r="G172" t="n">
+        <v>3</v>
+      </c>
+      <c r="H172" t="n">
         <v>3.38</v>
       </c>
-      <c r="F172" t="inlineStr"/>
-      <c r="G172" t="inlineStr"/>
-      <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr">
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr">
         <is>
           <t>xlsx</t>
         </is>
@@ -6377,21 +8285,36 @@
           <t>Combined</t>
         </is>
       </c>
-      <c r="C173" t="n">
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>data_raw/mar-2026-sme-results.pdf</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
         <v>3.13</v>
       </c>
-      <c r="D173" t="n">
-        <v>3</v>
-      </c>
-      <c r="E173" t="n">
+      <c r="G173" t="n">
+        <v>3</v>
+      </c>
+      <c r="H173" t="n">
         <v>3.38</v>
       </c>
-      <c r="F173" t="inlineStr"/>
-      <c r="G173" t="inlineStr"/>
-      <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr">
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr"/>
+      <c r="N173" t="inlineStr">
         <is>
           <t>xlsx</t>
         </is>
@@ -6408,21 +8331,36 @@
           <t>Combined</t>
         </is>
       </c>
-      <c r="C174" t="n">
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>data_raw/apr-2026-sme-results.pdf</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
         <v>3.13</v>
       </c>
-      <c r="D174" t="n">
-        <v>3</v>
-      </c>
-      <c r="E174" t="n">
+      <c r="G174" t="n">
+        <v>3</v>
+      </c>
+      <c r="H174" t="n">
         <v>3.38</v>
       </c>
-      <c r="F174" t="inlineStr"/>
-      <c r="G174" t="inlineStr"/>
-      <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr">
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr">
         <is>
           <t>xlsx</t>
         </is>
